--- a/_ForDRA/BVSimulationFiles/64.xlsx
+++ b/_ForDRA/BVSimulationFiles/64.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001339882121807466</v>
+        <v>0.02679764243614932</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001344483507393238</v>
+        <v>0.02688967014786476</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001349084892979009</v>
+        <v>0.02698169785958018</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001353686278564781</v>
+        <v>0.02707372557129562</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001358287664150553</v>
+        <v>0.02716575328301106</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001362889049736325</v>
+        <v>0.0272577809947265</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001367490435322097</v>
+        <v>0.02734980870644194</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001372091820907869</v>
+        <v>0.02744183641815738</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001376693206493641</v>
+        <v>0.02753386412987282</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001381294592079413</v>
+        <v>0.02762589184158826</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001385895977665185</v>
+        <v>0.0277179195533037</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001390497363250957</v>
+        <v>0.02780994726501914</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001395098748836728</v>
+        <v>0.02790197497673456</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0013997001344225</v>
+        <v>0.02799400268845</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001404301520008272</v>
+        <v>0.02808603040016544</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001408902905594044</v>
+        <v>0.02817805811188088</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001413504291179816</v>
+        <v>0.02827008582359632</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001418105676765588</v>
+        <v>0.02836211353531176</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00142270706235136</v>
+        <v>0.0284541412470272</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001427308447937131</v>
+        <v>0.02854616895874262</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001339882121807466</v>
+        <v>0.02679764243614932</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001344483507393238</v>
+        <v>0.02688967014786476</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001349084892979009</v>
+        <v>0.02698169785958018</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001353686278564781</v>
+        <v>0.02707372557129562</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001358287664150553</v>
+        <v>0.02716575328301106</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001362889049736325</v>
+        <v>0.0272577809947265</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001367490435322097</v>
+        <v>0.02734980870644194</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001372091820907869</v>
+        <v>0.02744183641815738</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001376693206493641</v>
+        <v>0.02753386412987282</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001381294592079413</v>
+        <v>0.02762589184158826</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001385895977665185</v>
+        <v>0.0277179195533037</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001390497363250957</v>
+        <v>0.02780994726501914</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001395098748836728</v>
+        <v>0.02790197497673456</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0013997001344225</v>
+        <v>0.02799400268845</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001404301520008272</v>
+        <v>0.02808603040016544</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001408902905594044</v>
+        <v>0.02817805811188088</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001413504291179816</v>
+        <v>0.02827008582359632</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001418105676765588</v>
+        <v>0.02836211353531176</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00142270706235136</v>
+        <v>0.0284541412470272</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001427308447937131</v>
+        <v>0.02854616895874262</v>
       </c>
     </row>
   </sheetData>
